--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2149,10 +2149,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97155205</v>
+        <v>134855725</v>
       </c>
       <c r="B15" t="n">
-        <v>97983</v>
+        <v>99112</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,41 +2160,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stakgölsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516810</v>
+        <v>516726</v>
       </c>
       <c r="R15" t="n">
-        <v>6538951</v>
+        <v>6538929</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2218,17 +2228,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>stort bestånd</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2237,29 +2242,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>108401900</v>
+        <v>97155205</v>
       </c>
       <c r="B16" t="n">
-        <v>96708</v>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2267,45 +2271,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tärnmossemon, Nrk</t>
+          <t>Stakgölsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520654</v>
+        <v>516810</v>
       </c>
       <c r="R16" t="n">
-        <v>6538974</v>
+        <v>6538951</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2329,22 +2329,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>stort bestånd</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,10 +2367,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62126985</v>
+        <v>108401900</v>
       </c>
       <c r="B17" t="n">
-        <v>97986</v>
+        <v>96708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2383,37 +2378,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skåle 0850/5550, Nrk</t>
+          <t>Tärnmossemon, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511839</v>
+        <v>520654</v>
       </c>
       <c r="R17" t="n">
-        <v>6538728</v>
+        <v>6538974</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2432,22 +2435,27 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Svennevad</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1984-12-12</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1984-12-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2456,28 +2464,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>98669244</v>
+        <v>62126985</v>
       </c>
       <c r="B18" t="n">
-        <v>96554</v>
+        <v>97986</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2485,49 +2494,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>221946</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gropadalen, Nrk</t>
+          <t>Skåle 0850/5550, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509662</v>
+        <v>511839</v>
       </c>
       <c r="R18" t="n">
-        <v>6538673</v>
+        <v>6538728</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2551,12 +2548,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>1984-12-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>1984-12-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2565,76 +2567,75 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135018500</v>
+        <v>98669244</v>
       </c>
       <c r="B19" t="n">
-        <v>58136</v>
+        <v>96554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hovdesjön. bäcken, Nrk</t>
+          <t>Gropadalen, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512422</v>
+        <v>509662</v>
       </c>
       <c r="R19" t="n">
-        <v>6538962</v>
+        <v>6538673</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2661,22 +2662,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2685,55 +2676,56 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135018493</v>
+        <v>135018500</v>
       </c>
       <c r="B20" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2822,10 +2814,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129810221</v>
+        <v>135018493</v>
       </c>
       <c r="B21" t="n">
-        <v>97394</v>
+        <v>58131</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,45 +2825,49 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>103023</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Aggsjön, Nrk</t>
+          <t>Hovdesjön. bäcken, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521076</v>
+        <v>512422</v>
       </c>
       <c r="R21" t="n">
-        <v>6538419</v>
+        <v>6538962</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2890,12 +2886,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Svennevad</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -2905,12 +2901,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2919,61 +2915,60 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129810223</v>
+        <v>129810221</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>97394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2590</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2981,10 +2976,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521077</v>
+        <v>521076</v>
       </c>
       <c r="R22" t="n">
-        <v>6538398</v>
+        <v>6538419</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3029,17 +3024,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mycket gamla hackmärken, men i ytterzonen (?) av etablerat revir</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3058,41 +3049,40 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129810219</v>
+        <v>129810223</v>
       </c>
       <c r="B23" t="n">
-        <v>4775</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3102,10 +3092,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521090</v>
+        <v>521077</v>
       </c>
       <c r="R23" t="n">
-        <v>6538419</v>
+        <v>6538398</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3150,13 +3140,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mycket gamla hackmärken, men i ytterzonen (?) av etablerat revir</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3175,10 +3169,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129810218</v>
+        <v>129810219</v>
       </c>
       <c r="B24" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3186,21 +3180,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3292,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129810217</v>
+        <v>129810218</v>
       </c>
       <c r="B25" t="n">
-        <v>97983</v>
+        <v>5179</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3303,31 +3297,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3335,10 +3330,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521141</v>
+        <v>521090</v>
       </c>
       <c r="R25" t="n">
-        <v>6538398</v>
+        <v>6538419</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3408,27 +3403,27 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67277679</v>
+        <v>129810217</v>
       </c>
       <c r="B26" t="n">
-        <v>109866</v>
+        <v>97983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220228</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3436,35 +3431,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kållslätt, 525 m NNO om, Nrk</t>
+          <t>Aggsjön, Nrk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510443</v>
+        <v>521141</v>
       </c>
       <c r="R26" t="n">
-        <v>6538515</v>
+        <v>6538398</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3483,22 +3471,27 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Hal-0031</t>
+          <t>Svennevad</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3507,37 +3500,29 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Skogsvägkant</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128760477</v>
+        <v>67277679</v>
       </c>
       <c r="B27" t="n">
-        <v>93197</v>
+        <v>109866</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3545,44 +3530,52 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220228</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gruvemon, Nrk</t>
+          <t>Kållslätt, 525 m NNO om, Nrk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517886</v>
+        <v>510443</v>
       </c>
       <c r="R27" t="n">
-        <v>6536773</v>
+        <v>6538515</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3601,27 +3594,22 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Svennevad</t>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Hal-0031</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3630,29 +3618,37 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Skogsvägkant</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120432305</v>
+        <v>128760477</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3660,44 +3656,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fåglamossatärnen, Fåglamossen-Bavlingebäcken, Nrk</t>
+          <t>Gruvemon, Nrk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518189</v>
+        <v>517886</v>
       </c>
       <c r="R28" t="n">
-        <v>6536658</v>
+        <v>6536773</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3721,22 +3717,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3764,10 +3760,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120432283</v>
+        <v>120432305</v>
       </c>
       <c r="B29" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3775,21 +3771,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3879,7 +3875,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120432395</v>
+        <v>120432283</v>
       </c>
       <c r="B30" t="n">
         <v>79946</v>
@@ -3917,14 +3913,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fåglamossen, Nrk</t>
+          <t>Fåglamossatärnen, Fåglamossen-Bavlingebäcken, Nrk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518363</v>
+        <v>518189</v>
       </c>
       <c r="R30" t="n">
-        <v>6536679</v>
+        <v>6536658</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3994,53 +3990,52 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115463834</v>
+        <v>120432395</v>
       </c>
       <c r="B31" t="n">
-        <v>97394</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2590</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ommekärrsmossen, Nrk</t>
+          <t>Fåglamossen, Nrk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521356</v>
+        <v>518363</v>
       </c>
       <c r="R31" t="n">
-        <v>6536843</v>
+        <v>6536679</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4067,22 +4062,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4110,7 +4105,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115464064</v>
+        <v>115463834</v>
       </c>
       <c r="B32" t="n">
         <v>97394</v>
@@ -4153,10 +4148,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521284</v>
+        <v>521356</v>
       </c>
       <c r="R32" t="n">
-        <v>6536870</v>
+        <v>6536843</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4226,10 +4221,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115463863</v>
+        <v>115464064</v>
       </c>
       <c r="B33" t="n">
-        <v>92333</v>
+        <v>97394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4237,30 +4232,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4217</v>
+        <v>2590</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4268,10 +4264,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521375</v>
+        <v>521284</v>
       </c>
       <c r="R33" t="n">
-        <v>6536833</v>
+        <v>6536870</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4341,10 +4337,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115463816</v>
+        <v>115463863</v>
       </c>
       <c r="B34" t="n">
-        <v>5179</v>
+        <v>92333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4352,32 +4348,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>4217</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4385,10 +4379,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521348</v>
+        <v>521375</v>
       </c>
       <c r="R34" t="n">
-        <v>6536870</v>
+        <v>6536833</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4458,10 +4452,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120635109</v>
+        <v>115463816</v>
       </c>
       <c r="B35" t="n">
-        <v>97394</v>
+        <v>5179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4469,42 +4463,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Ommekärrsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517608</v>
+        <v>521348</v>
       </c>
       <c r="R35" t="n">
-        <v>6536616</v>
+        <v>6536870</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4531,22 +4526,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4574,10 +4569,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120635189</v>
+        <v>120635109</v>
       </c>
       <c r="B36" t="n">
-        <v>91872</v>
+        <v>97394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4585,41 +4580,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517634</v>
+        <v>517608</v>
       </c>
       <c r="R36" t="n">
-        <v>6536147</v>
+        <v>6536616</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4689,38 +4685,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120635175</v>
+        <v>120635189</v>
       </c>
       <c r="B37" t="n">
-        <v>93235</v>
+        <v>91872</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -4731,10 +4727,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>517662</v>
+        <v>517634</v>
       </c>
       <c r="R37" t="n">
-        <v>6536294</v>
+        <v>6536147</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4804,10 +4800,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120635132</v>
+        <v>120635175</v>
       </c>
       <c r="B38" t="n">
-        <v>75428</v>
+        <v>93235</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4815,41 +4811,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Molångskärret, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>517612</v>
+        <v>517662</v>
       </c>
       <c r="R38" t="n">
-        <v>6536339</v>
+        <v>6536294</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4919,10 +4915,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120635182</v>
+        <v>120635132</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>75428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4930,21 +4926,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4957,14 +4953,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Molångskärret, Nrk</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>517625</v>
+        <v>517612</v>
       </c>
       <c r="R39" t="n">
-        <v>6536200</v>
+        <v>6536339</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5034,10 +5030,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120635185</v>
+        <v>120635182</v>
       </c>
       <c r="B40" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5045,21 +5041,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5076,10 +5072,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>517623</v>
+        <v>517625</v>
       </c>
       <c r="R40" t="n">
-        <v>6536181</v>
+        <v>6536200</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5149,43 +5145,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120635120</v>
+        <v>120635185</v>
       </c>
       <c r="B41" t="n">
-        <v>4775</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100299</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5193,10 +5187,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>517619</v>
+        <v>517623</v>
       </c>
       <c r="R41" t="n">
-        <v>6536384</v>
+        <v>6536181</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5266,10 +5260,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120635095</v>
+        <v>120635120</v>
       </c>
       <c r="B42" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5277,21 +5271,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5306,14 +5300,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>517618</v>
+        <v>517619</v>
       </c>
       <c r="R42" t="n">
-        <v>6536590</v>
+        <v>6536384</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5383,7 +5377,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120635096</v>
+        <v>120635095</v>
       </c>
       <c r="B43" t="n">
         <v>5179</v>
@@ -5427,10 +5421,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>517630</v>
+        <v>517618</v>
       </c>
       <c r="R43" t="n">
-        <v>6536573</v>
+        <v>6536590</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5500,7 +5494,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120635118</v>
+        <v>120635096</v>
       </c>
       <c r="B44" t="n">
         <v>5179</v>
@@ -5540,14 +5534,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>517614</v>
+        <v>517630</v>
       </c>
       <c r="R44" t="n">
-        <v>6536378</v>
+        <v>6536573</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5617,7 +5611,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120635184</v>
+        <v>120635118</v>
       </c>
       <c r="B45" t="n">
         <v>5179</v>
@@ -5661,10 +5655,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>517640</v>
+        <v>517614</v>
       </c>
       <c r="R45" t="n">
-        <v>6536207</v>
+        <v>6536378</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5734,32 +5728,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120635188</v>
+        <v>120635184</v>
       </c>
       <c r="B46" t="n">
-        <v>5495</v>
+        <v>5179</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101410</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5768,7 +5762,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5778,10 +5772,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>517619</v>
+        <v>517640</v>
       </c>
       <c r="R46" t="n">
-        <v>6536148</v>
+        <v>6536207</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5851,10 +5845,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120635114</v>
+        <v>120635188</v>
       </c>
       <c r="B47" t="n">
-        <v>5178</v>
+        <v>5495</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5862,21 +5856,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102204</v>
+        <v>101410</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5891,14 +5885,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Molångskärret, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>517596</v>
+        <v>517619</v>
       </c>
       <c r="R47" t="n">
-        <v>6536395</v>
+        <v>6536148</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5968,32 +5962,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120635124</v>
+        <v>120635114</v>
       </c>
       <c r="B48" t="n">
-        <v>4781</v>
+        <v>5178</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102306</v>
+        <v>102204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6002,20 +5996,20 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Molångskärret, Nrk</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>517623</v>
+        <v>517596</v>
       </c>
       <c r="R48" t="n">
-        <v>6536362</v>
+        <v>6536395</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6058,11 +6052,6 @@
       <c r="AB48" t="inlineStr">
         <is>
           <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6090,10 +6079,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120635104</v>
+        <v>120635124</v>
       </c>
       <c r="B49" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6101,21 +6090,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6124,20 +6113,20 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>517609</v>
+        <v>517623</v>
       </c>
       <c r="R49" t="n">
-        <v>6536542</v>
+        <v>6536362</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6180,6 +6169,11 @@
       <c r="AB49" t="inlineStr">
         <is>
           <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6207,7 +6201,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120635119</v>
+        <v>120635104</v>
       </c>
       <c r="B50" t="n">
         <v>5199</v>
@@ -6241,20 +6235,20 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>517619</v>
+        <v>517609</v>
       </c>
       <c r="R50" t="n">
-        <v>6536384</v>
+        <v>6536542</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6324,7 +6318,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120635176</v>
+        <v>120635119</v>
       </c>
       <c r="B51" t="n">
         <v>5199</v>
@@ -6358,7 +6352,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6368,10 +6362,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>517661</v>
+        <v>517619</v>
       </c>
       <c r="R51" t="n">
-        <v>6536283</v>
+        <v>6536384</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6441,7 +6435,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120635190</v>
+        <v>120635176</v>
       </c>
       <c r="B52" t="n">
         <v>5199</v>
@@ -6485,10 +6479,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>517634</v>
+        <v>517661</v>
       </c>
       <c r="R52" t="n">
-        <v>6536147</v>
+        <v>6536283</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6558,10 +6552,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120635112</v>
+        <v>120635190</v>
       </c>
       <c r="B53" t="n">
-        <v>97983</v>
+        <v>5199</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6569,42 +6563,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>517607</v>
+        <v>517634</v>
       </c>
       <c r="R53" t="n">
-        <v>6536479</v>
+        <v>6536147</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6674,52 +6669,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120635183</v>
+        <v>120635112</v>
       </c>
       <c r="B54" t="n">
-        <v>79085</v>
+        <v>97983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>517625</v>
+        <v>517607</v>
       </c>
       <c r="R54" t="n">
-        <v>6536200</v>
+        <v>6536479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6789,57 +6785,55 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132585613</v>
+        <v>120635183</v>
       </c>
       <c r="B55" t="n">
-        <v>40305</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>214803</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kortorpa mosse, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515594</v>
+        <v>517625</v>
       </c>
       <c r="R55" t="n">
-        <v>6537089</v>
+        <v>6536200</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6863,12 +6857,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6896,45 +6900,54 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>85451244</v>
+        <v>132585613</v>
       </c>
       <c r="B56" t="n">
-        <v>97358</v>
+        <v>40305</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>214803</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Kortorpa mosse, Nrk</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519672</v>
+        <v>515594</v>
       </c>
       <c r="R56" t="n">
-        <v>6532590</v>
+        <v>6537089</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -6961,12 +6974,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6975,25 +6988,26 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>85451245</v>
+        <v>85451244</v>
       </c>
       <c r="B57" t="n">
         <v>97358</v>
@@ -7028,10 +7042,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519625</v>
+        <v>519672</v>
       </c>
       <c r="R57" t="n">
-        <v>6532581</v>
+        <v>6532590</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7090,10 +7104,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>55321736</v>
+        <v>85451245</v>
       </c>
       <c r="B58" t="n">
-        <v>78993</v>
+        <v>97358</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7101,41 +7115,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519636</v>
+        <v>519625</v>
       </c>
       <c r="R58" t="n">
-        <v>6532709</v>
+        <v>6532581</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7159,17 +7169,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7182,67 +7187,66 @@
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>85451302</v>
+        <v>55321736</v>
       </c>
       <c r="B59" t="n">
-        <v>96458</v>
+        <v>78993</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2818</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519731</v>
+        <v>519636</v>
       </c>
       <c r="R59" t="n">
-        <v>6532645</v>
+        <v>6532709</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7266,12 +7270,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7284,24 +7293,29 @@
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>85451356</v>
+        <v>85451302</v>
       </c>
       <c r="B60" t="n">
-        <v>92333</v>
+        <v>96458</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7309,21 +7323,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4217</v>
+        <v>2818</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7333,10 +7347,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519697</v>
+        <v>519731</v>
       </c>
       <c r="R60" t="n">
-        <v>6532776</v>
+        <v>6532645</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7395,48 +7409,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>54013950</v>
+        <v>85451356</v>
       </c>
       <c r="B61" t="n">
-        <v>93197</v>
+        <v>92333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519596</v>
+        <v>519697</v>
       </c>
       <c r="R61" t="n">
-        <v>6532710</v>
+        <v>6532776</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7460,12 +7474,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7477,23 +7491,22 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AR61" t="inlineStr"/>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>81095228</v>
+        <v>54013950</v>
       </c>
       <c r="B62" t="n">
         <v>93197</v>
@@ -7524,14 +7537,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hjärtasjön med omnejd, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519615</v>
+        <v>519596</v>
       </c>
       <c r="R62" t="n">
-        <v>6532734</v>
+        <v>6532710</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7558,12 +7571,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7575,60 +7588,61 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AR62" t="inlineStr"/>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>54013984</v>
+        <v>81095228</v>
       </c>
       <c r="B63" t="n">
-        <v>91282</v>
+        <v>93197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>Hjärtasjön med omnejd, Nrk</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519636</v>
+        <v>519615</v>
       </c>
       <c r="R63" t="n">
-        <v>6532709</v>
+        <v>6532734</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7655,12 +7669,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7672,71 +7686,63 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AR63" t="inlineStr"/>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132028911</v>
+        <v>54013984</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>91282</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bavlingeskogen, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519619</v>
+        <v>519636</v>
       </c>
       <c r="R64" t="n">
-        <v>6532722</v>
+        <v>6532709</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7760,12 +7766,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7774,71 +7780,74 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AR64" t="inlineStr"/>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>55321959</v>
+        <v>132028911</v>
       </c>
       <c r="B65" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>Bavlingeskogen, Nrk</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519636</v>
+        <v>519619</v>
       </c>
       <c r="R65" t="n">
-        <v>6532709</v>
+        <v>6532722</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7862,17 +7871,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7881,30 +7885,26 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>55321978</v>
+        <v>55321959</v>
       </c>
       <c r="B66" t="n">
         <v>79946</v>
@@ -7943,10 +7943,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519596</v>
+        <v>519636</v>
       </c>
       <c r="R66" t="n">
-        <v>6532710</v>
+        <v>6532709</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8015,7 +8015,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>55322041</v>
+        <v>55321978</v>
       </c>
       <c r="B67" t="n">
         <v>79946</v>
@@ -8054,10 +8054,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519628</v>
+        <v>519596</v>
       </c>
       <c r="R67" t="n">
-        <v>6532734</v>
+        <v>6532710</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Observerad av Toni Berglund</t>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8126,7 +8126,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>85451274</v>
+        <v>55322041</v>
       </c>
       <c r="B68" t="n">
         <v>79946</v>
@@ -8154,20 +8154,24 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519738</v>
+        <v>519628</v>
       </c>
       <c r="R68" t="n">
-        <v>6532781</v>
+        <v>6532734</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8191,12 +8195,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Observerad av Toni Berglund</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8209,24 +8218,29 @@
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>85451350</v>
+        <v>85451274</v>
       </c>
       <c r="B69" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8234,21 +8248,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8258,10 +8272,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520143</v>
+        <v>519738</v>
       </c>
       <c r="R69" t="n">
-        <v>6532731</v>
+        <v>6532781</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8320,10 +8334,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>85451285</v>
+        <v>85451350</v>
       </c>
       <c r="B70" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8331,21 +8345,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8355,10 +8369,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520192</v>
+        <v>520143</v>
       </c>
       <c r="R70" t="n">
-        <v>6532728</v>
+        <v>6532731</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8417,7 +8431,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>85451403</v>
+        <v>85451285</v>
       </c>
       <c r="B71" t="n">
         <v>79946</v>
@@ -8448,14 +8462,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>ost Bavlingssjön, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520311</v>
+        <v>520192</v>
       </c>
       <c r="R71" t="n">
-        <v>6532603</v>
+        <v>6532728</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8514,48 +8528,48 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>80563800</v>
+        <v>85451403</v>
       </c>
       <c r="B72" t="n">
-        <v>93193</v>
+        <v>79946</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4363</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>ost Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519723</v>
+        <v>520311</v>
       </c>
       <c r="R72" t="n">
-        <v>6531341</v>
+        <v>6532603</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8579,12 +8593,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8599,44 +8613,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>80563801</v>
+        <v>80563800</v>
       </c>
       <c r="B73" t="n">
-        <v>93197</v>
+        <v>93193</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8646,10 +8660,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519697</v>
+        <v>519723</v>
       </c>
       <c r="R73" t="n">
-        <v>6531333</v>
+        <v>6531341</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8708,7 +8722,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>80563803</v>
+        <v>80563801</v>
       </c>
       <c r="B74" t="n">
         <v>93197</v>
@@ -8743,10 +8757,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519682</v>
+        <v>519697</v>
       </c>
       <c r="R74" t="n">
-        <v>6531348</v>
+        <v>6531333</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8805,7 +8819,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>80563804</v>
+        <v>80563803</v>
       </c>
       <c r="B75" t="n">
         <v>93197</v>
@@ -8840,10 +8854,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519675</v>
+        <v>519682</v>
       </c>
       <c r="R75" t="n">
-        <v>6531363</v>
+        <v>6531348</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8902,7 +8916,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>80563805</v>
+        <v>80563804</v>
       </c>
       <c r="B76" t="n">
         <v>93197</v>
@@ -8937,10 +8951,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519682</v>
+        <v>519675</v>
       </c>
       <c r="R76" t="n">
-        <v>6531371</v>
+        <v>6531363</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8999,45 +9013,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>54014169</v>
+        <v>80563805</v>
       </c>
       <c r="B77" t="n">
-        <v>91872</v>
+        <v>93197</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519821</v>
+        <v>519682</v>
       </c>
       <c r="R77" t="n">
-        <v>6531449</v>
+        <v>6531371</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9064,12 +9078,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9081,23 +9095,22 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AR77" t="inlineStr"/>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>85451261</v>
+        <v>54014169</v>
       </c>
       <c r="B78" t="n">
         <v>91872</v>
@@ -9128,17 +9141,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519855</v>
+        <v>519821</v>
       </c>
       <c r="R78" t="n">
-        <v>6531422</v>
+        <v>6531449</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9162,12 +9175,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9179,67 +9192,64 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
+      <c r="AR78" t="inlineStr"/>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>55322013</v>
+        <v>85451261</v>
       </c>
       <c r="B79" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519789</v>
+        <v>519855</v>
       </c>
       <c r="R79" t="n">
-        <v>6531472</v>
+        <v>6531422</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9263,17 +9273,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9286,26 +9291,21 @@
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>80563802</v>
+        <v>55322013</v>
       </c>
       <c r="B80" t="n">
         <v>79946</v>
@@ -9333,17 +9333,21 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519687</v>
+        <v>519789</v>
       </c>
       <c r="R80" t="n">
-        <v>6531345</v>
+        <v>6531472</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9370,12 +9374,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9387,27 +9396,27 @@
       <c r="AG80" t="b">
         <v>0</v>
       </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>silverstubbe</t>
-        </is>
-      </c>
       <c r="AT80" t="inlineStr"/>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>85451281</v>
+        <v>80563802</v>
       </c>
       <c r="B81" t="n">
         <v>79946</v>
@@ -9438,17 +9447,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>519882</v>
+        <v>519687</v>
       </c>
       <c r="R81" t="n">
-        <v>6531425</v>
+        <v>6531345</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9472,12 +9481,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9488,19 +9497,121 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>silverstubbe</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>85451281</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>väst Bavlingssjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>519882</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6531425</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2020-05-03</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2020-05-15</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
+      <c r="AX82" t="inlineStr">
         <is>
           <t>Mikael Hagström</t>
         </is>
       </c>
-      <c r="AY81" t="inlineStr"/>
+      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY82"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -785,6 +790,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109135798</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115624388</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102170702</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62868832</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4798866</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123868390</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1448,6 +1483,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62126968</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115377672</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1680,6 +1725,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115377556</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1797,6 +1847,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115377695</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1914,6 +1969,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115377558</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2030,6 +2090,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129810216</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2146,6 +2211,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133708635</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2257,6 +2327,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134855725</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2364,6 +2439,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97155205</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2480,6 +2560,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108401900</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2582,6 +2667,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62126985</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2692,6 +2782,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98669244</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2811,6 +2906,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135018500</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2930,6 +3030,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135018493</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3046,6 +3151,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129810221</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3166,6 +3276,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129810223</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3283,6 +3398,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129810219</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3400,6 +3520,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129810218</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3516,6 +3641,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129810217</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3642,6 +3772,11 @@
           <t>Arkiv Floraväktarlokaler</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/67277679</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3757,6 +3892,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128760477</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3872,6 +4012,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120432305</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3987,6 +4132,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120432283</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4102,6 +4252,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120432395</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4218,6 +4373,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115463834</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4334,6 +4494,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115464064</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4449,6 +4614,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115463863</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4566,6 +4736,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115463816</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4682,6 +4857,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635109</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4797,6 +4977,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635189</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4912,6 +5097,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635175</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5027,6 +5217,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635132</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5142,6 +5337,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635182</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5257,6 +5457,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635185</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5374,6 +5579,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635120</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5491,6 +5701,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635095</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5608,6 +5823,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635096</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5725,6 +5945,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635118</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5842,6 +6067,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635184</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5959,6 +6189,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635188</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6076,6 +6311,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635114</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6198,6 +6438,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635124</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6315,6 +6560,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635104</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6432,6 +6682,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635119</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6549,6 +6804,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635176</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6666,6 +6926,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635190</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6782,6 +7047,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635112</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6897,6 +7167,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120635183</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7004,6 +7279,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132585613</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7101,6 +7381,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451244</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7198,6 +7483,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451245</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7309,6 +7599,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55321736</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7406,6 +7701,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451302</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7503,6 +7803,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451356</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7601,6 +7906,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54013950</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7698,6 +8008,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/81095228</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7796,6 +8111,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54013984</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7901,6 +8221,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132028911</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8012,6 +8337,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55321959</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8123,6 +8453,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55321978</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8234,6 +8569,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55322041</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8331,6 +8671,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451274</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8428,6 +8773,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451350</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8525,6 +8875,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451285</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8622,6 +8977,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451403</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8719,6 +9079,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563800</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8816,6 +9181,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563801</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8913,6 +9283,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563803</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9010,6 +9385,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563804</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9107,6 +9487,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563805</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9205,6 +9590,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54014169</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9302,6 +9692,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451261</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9413,6 +9808,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55322013</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9515,6 +9915,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563802</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9612,8 +10017,96 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85451281</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -2222,7 +2222,7 @@
         <v>134855725</v>
       </c>
       <c r="B15" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
         <v>135018500</v>
       </c>
       <c r="B20" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         <v>135018493</v>
       </c>
       <c r="B21" t="n">
-        <v>58131</v>
+        <v>58136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -2222,7 +2222,7 @@
         <v>134855725</v>
       </c>
       <c r="B15" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ81"/>
+  <dimension ref="A1:AZ82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2219,10 +2219,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>97155205</v>
+        <v>134855725</v>
       </c>
       <c r="B15" t="n">
-        <v>97983</v>
+        <v>99191</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2230,41 +2230,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stakgölsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>516810</v>
+        <v>516726</v>
       </c>
       <c r="R15" t="n">
-        <v>6538951</v>
+        <v>6538929</v>
       </c>
       <c r="S15" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2288,17 +2298,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2021-11-14</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>stort bestånd</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,34 +2312,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97155205</t>
+          <t>https://artportalen.se/Sighting/134855725</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>108401900</v>
+        <v>97155205</v>
       </c>
       <c r="B16" t="n">
-        <v>96708</v>
+        <v>97983</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2342,45 +2346,41 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Tärnmossemon, Nrk</t>
+          <t>Stakgölsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520654</v>
+        <v>516810</v>
       </c>
       <c r="R16" t="n">
-        <v>6538974</v>
+        <v>6538951</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2404,22 +2404,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>08:30</t>
+          <t>2021-11-14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:45</t>
+          <t>2021-11-14</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>stort bestånd</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2446,16 +2441,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/108401900</t>
+          <t>https://artportalen.se/Sighting/97155205</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>62126985</v>
+        <v>108401900</v>
       </c>
       <c r="B17" t="n">
-        <v>97986</v>
+        <v>96708</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2463,37 +2458,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221946</v>
+        <v>2180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skåle 0850/5550, Nrk</t>
+          <t>Tärnmossemon, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>511839</v>
+        <v>520654</v>
       </c>
       <c r="R17" t="n">
-        <v>6538728</v>
+        <v>6538974</v>
       </c>
       <c r="S17" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2512,22 +2515,27 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
+          <t>Svennevad</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>1984-12-12</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>1984-12-12</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Sparsamt</t>
+          <t>2023-04-23</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2536,33 +2544,34 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Gunnar Hallin</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/62126985</t>
+          <t>https://artportalen.se/Sighting/108401900</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>98669244</v>
+        <v>62126985</v>
       </c>
       <c r="B18" t="n">
-        <v>96554</v>
+        <v>97986</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2570,49 +2579,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>210</v>
+        <v>221946</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Gropadalen, Nrk</t>
+          <t>Skåle 0850/5550, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>509662</v>
+        <v>511839</v>
       </c>
       <c r="R18" t="n">
-        <v>6538673</v>
+        <v>6538728</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2636,12 +2633,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>1984-12-12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-02-18</t>
+          <t>1984-12-12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Sparsamt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2650,81 +2652,80 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Gunnar Hallin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/98669244</t>
+          <t>https://artportalen.se/Sighting/62126985</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135018500</v>
+        <v>98669244</v>
       </c>
       <c r="B19" t="n">
-        <v>58141</v>
+        <v>96554</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>210</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>kapslar</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hovdesjön. bäcken, Nrk</t>
+          <t>Gropadalen, Nrk</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>512422</v>
+        <v>509662</v>
       </c>
       <c r="R19" t="n">
-        <v>6538962</v>
+        <v>6538673</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2751,22 +2752,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2022-02-18</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2775,60 +2766,61 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Helena Johansson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135018500</t>
+          <t>https://artportalen.se/Sighting/98669244</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135018493</v>
+        <v>135018500</v>
       </c>
       <c r="B20" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -2916,16 +2908,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135018493</t>
+          <t>https://artportalen.se/Sighting/135018500</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129810221</v>
+        <v>135018493</v>
       </c>
       <c r="B21" t="n">
-        <v>97394</v>
+        <v>58136</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,45 +2925,49 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>103023</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Aggsjön, Nrk</t>
+          <t>Hovdesjön. bäcken, Nrk</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>521076</v>
+        <v>512422</v>
       </c>
       <c r="R21" t="n">
-        <v>6538419</v>
+        <v>6538962</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2990,12 +2986,12 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Svennevad</t>
+          <t>Hallsberg</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
@@ -3005,12 +3001,12 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3019,66 +3015,65 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Helena Johansson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810221</t>
+          <t>https://artportalen.se/Sighting/135018493</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129810223</v>
+        <v>129810221</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>97394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>2590</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3086,10 +3081,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>521077</v>
+        <v>521076</v>
       </c>
       <c r="R22" t="n">
-        <v>6538398</v>
+        <v>6538419</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3134,17 +3129,13 @@
           <t>12:00</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mycket gamla hackmärken, men i ytterzonen (?) av etablerat revir</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3162,47 +3153,46 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810223</t>
+          <t>https://artportalen.se/Sighting/129810221</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129810219</v>
+        <v>129810223</v>
       </c>
       <c r="B23" t="n">
-        <v>4775</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
@@ -3212,10 +3202,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>521090</v>
+        <v>521077</v>
       </c>
       <c r="R23" t="n">
-        <v>6538419</v>
+        <v>6538398</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3260,13 +3250,17 @@
           <t>12:00</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Mycket gamla hackmärken, men i ytterzonen (?) av etablerat revir</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3284,16 +3278,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810219</t>
+          <t>https://artportalen.se/Sighting/129810223</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129810218</v>
+        <v>129810219</v>
       </c>
       <c r="B24" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3301,21 +3295,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3406,16 +3400,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810218</t>
+          <t>https://artportalen.se/Sighting/129810219</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129810217</v>
+        <v>129810218</v>
       </c>
       <c r="B25" t="n">
-        <v>97983</v>
+        <v>5179</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3423,31 +3417,32 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3455,10 +3450,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>521141</v>
+        <v>521090</v>
       </c>
       <c r="R25" t="n">
-        <v>6538398</v>
+        <v>6538419</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3527,33 +3522,33 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129810217</t>
+          <t>https://artportalen.se/Sighting/129810218</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>67277679</v>
+        <v>129810217</v>
       </c>
       <c r="B26" t="n">
-        <v>109866</v>
+        <v>97983</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220228</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sommarfibbla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leontodon hispidus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -3561,35 +3556,28 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Kållslätt, 525 m NNO om, Nrk</t>
+          <t>Aggsjön, Nrk</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>510443</v>
+        <v>521141</v>
       </c>
       <c r="R26" t="n">
-        <v>6538515</v>
+        <v>6538398</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3608,22 +3596,27 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>Hallsberg</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>Arkiv-T-Hal-0031</t>
+          <t>Svennevad</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2016-07-11</t>
+          <t>2025-11-23</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3632,42 +3625,34 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Skogsvägkant</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>Arkiv Floraväktarlokaler</t>
-        </is>
-      </c>
+          <t>Per Karlsson Linderum</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/67277679</t>
+          <t>https://artportalen.se/Sighting/129810217</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128760477</v>
+        <v>67277679</v>
       </c>
       <c r="B27" t="n">
-        <v>93197</v>
+        <v>109866</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3675,44 +3660,52 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220228</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Sommarfibbla</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leontodon hispidus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Gruvemon, Nrk</t>
+          <t>Kållslätt, 525 m NNO om, Nrk</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>517886</v>
+        <v>510443</v>
       </c>
       <c r="R27" t="n">
-        <v>6536773</v>
+        <v>6538515</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3731,27 +3724,22 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>Svennevad</t>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Arkiv-T-Hal-0031</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>08:00</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>11:30</t>
+          <t>2016-07-11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3760,34 +3748,42 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Skogsvägkant</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Owe Nilsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Arkiv Floraväktarlokaler</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128760477</t>
+          <t>https://artportalen.se/Sighting/67277679</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120432305</v>
+        <v>128760477</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>93197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3795,44 +3791,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Fåglamossatärnen, Fåglamossen-Bavlingebäcken, Nrk</t>
+          <t>Gruvemon, Nrk</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518189</v>
+        <v>517886</v>
       </c>
       <c r="R28" t="n">
-        <v>6536658</v>
+        <v>6536773</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3856,22 +3852,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2025-09-28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3898,16 +3894,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120432305</t>
+          <t>https://artportalen.se/Sighting/128760477</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>120432283</v>
+        <v>120432305</v>
       </c>
       <c r="B29" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3915,21 +3911,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -4018,13 +4014,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120432283</t>
+          <t>https://artportalen.se/Sighting/120432305</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120432395</v>
+        <v>120432283</v>
       </c>
       <c r="B30" t="n">
         <v>79946</v>
@@ -4062,14 +4058,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Fåglamossen, Nrk</t>
+          <t>Fåglamossatärnen, Fåglamossen-Bavlingebäcken, Nrk</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518363</v>
+        <v>518189</v>
       </c>
       <c r="R30" t="n">
-        <v>6536679</v>
+        <v>6536658</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4138,59 +4134,58 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120432395</t>
+          <t>https://artportalen.se/Sighting/120432283</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>115463834</v>
+        <v>120432395</v>
       </c>
       <c r="B31" t="n">
-        <v>97394</v>
+        <v>79946</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2590</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ommekärrsmossen, Nrk</t>
+          <t>Fåglamossen, Nrk</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>521356</v>
+        <v>518363</v>
       </c>
       <c r="R31" t="n">
-        <v>6536843</v>
+        <v>6536679</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4217,22 +4212,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-03-28</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4259,13 +4254,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115463834</t>
+          <t>https://artportalen.se/Sighting/120432395</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>115464064</v>
+        <v>115463834</v>
       </c>
       <c r="B32" t="n">
         <v>97394</v>
@@ -4308,10 +4303,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>521284</v>
+        <v>521356</v>
       </c>
       <c r="R32" t="n">
-        <v>6536870</v>
+        <v>6536843</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4380,16 +4375,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115464064</t>
+          <t>https://artportalen.se/Sighting/115463834</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>115463863</v>
+        <v>115464064</v>
       </c>
       <c r="B33" t="n">
-        <v>92333</v>
+        <v>97394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4397,30 +4392,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4217</v>
+        <v>2590</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4428,10 +4424,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>521375</v>
+        <v>521284</v>
       </c>
       <c r="R33" t="n">
-        <v>6536833</v>
+        <v>6536870</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4500,16 +4496,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115463863</t>
+          <t>https://artportalen.se/Sighting/115464064</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>115463816</v>
+        <v>115463863</v>
       </c>
       <c r="B34" t="n">
-        <v>5179</v>
+        <v>92333</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4517,32 +4513,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100526</v>
+        <v>4217</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4550,10 +4544,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>521348</v>
+        <v>521375</v>
       </c>
       <c r="R34" t="n">
-        <v>6536870</v>
+        <v>6536833</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4622,16 +4616,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115463816</t>
+          <t>https://artportalen.se/Sighting/115463863</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>120635109</v>
+        <v>115463816</v>
       </c>
       <c r="B35" t="n">
-        <v>97394</v>
+        <v>5179</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4639,42 +4633,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2590</v>
+        <v>100526</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Ommekärrsmossen, Nrk</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>517608</v>
+        <v>521348</v>
       </c>
       <c r="R35" t="n">
-        <v>6536616</v>
+        <v>6536870</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4701,22 +4696,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-03-28</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4743,16 +4738,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635109</t>
+          <t>https://artportalen.se/Sighting/115463816</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>120635189</v>
+        <v>120635109</v>
       </c>
       <c r="B36" t="n">
-        <v>91872</v>
+        <v>97394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4760,41 +4755,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
-          <t>mycel</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>517634</v>
+        <v>517608</v>
       </c>
       <c r="R36" t="n">
-        <v>6536147</v>
+        <v>6536616</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4863,44 +4859,44 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635189</t>
+          <t>https://artportalen.se/Sighting/120635109</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>120635175</v>
+        <v>120635189</v>
       </c>
       <c r="B37" t="n">
-        <v>93235</v>
+        <v>91872</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
@@ -4911,10 +4907,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>517662</v>
+        <v>517634</v>
       </c>
       <c r="R37" t="n">
-        <v>6536294</v>
+        <v>6536147</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4983,16 +4979,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635175</t>
+          <t>https://artportalen.se/Sighting/120635189</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>120635132</v>
+        <v>120635175</v>
       </c>
       <c r="B38" t="n">
-        <v>75428</v>
+        <v>93235</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5000,41 +4996,41 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6426</v>
+        <v>5966</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Molångskärret, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>517612</v>
+        <v>517662</v>
       </c>
       <c r="R38" t="n">
-        <v>6536339</v>
+        <v>6536294</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5103,16 +5099,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635132</t>
+          <t>https://artportalen.se/Sighting/120635175</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>120635182</v>
+        <v>120635132</v>
       </c>
       <c r="B39" t="n">
-        <v>79084</v>
+        <v>75428</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5120,21 +5116,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6426</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5147,14 +5143,14 @@
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Molångskärret, Nrk</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>517625</v>
+        <v>517612</v>
       </c>
       <c r="R39" t="n">
-        <v>6536200</v>
+        <v>6536339</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5223,16 +5219,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635182</t>
+          <t>https://artportalen.se/Sighting/120635132</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>120635185</v>
+        <v>120635182</v>
       </c>
       <c r="B40" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5240,21 +5236,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5271,10 +5267,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>517623</v>
+        <v>517625</v>
       </c>
       <c r="R40" t="n">
-        <v>6536181</v>
+        <v>6536200</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5343,49 +5339,47 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635185</t>
+          <t>https://artportalen.se/Sighting/120635182</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120635120</v>
+        <v>120635185</v>
       </c>
       <c r="B41" t="n">
-        <v>4775</v>
+        <v>79946</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100299</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5393,10 +5387,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>517619</v>
+        <v>517623</v>
       </c>
       <c r="R41" t="n">
-        <v>6536384</v>
+        <v>6536181</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5465,16 +5459,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635120</t>
+          <t>https://artportalen.se/Sighting/120635185</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120635095</v>
+        <v>120635120</v>
       </c>
       <c r="B42" t="n">
-        <v>5179</v>
+        <v>4775</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5482,21 +5476,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>100299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5511,14 +5505,14 @@
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>517618</v>
+        <v>517619</v>
       </c>
       <c r="R42" t="n">
-        <v>6536590</v>
+        <v>6536384</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5587,13 +5581,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635095</t>
+          <t>https://artportalen.se/Sighting/120635120</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120635096</v>
+        <v>120635095</v>
       </c>
       <c r="B43" t="n">
         <v>5179</v>
@@ -5637,10 +5631,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>517630</v>
+        <v>517618</v>
       </c>
       <c r="R43" t="n">
-        <v>6536573</v>
+        <v>6536590</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5709,13 +5703,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635096</t>
+          <t>https://artportalen.se/Sighting/120635095</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120635118</v>
+        <v>120635096</v>
       </c>
       <c r="B44" t="n">
         <v>5179</v>
@@ -5755,14 +5749,14 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>517614</v>
+        <v>517630</v>
       </c>
       <c r="R44" t="n">
-        <v>6536378</v>
+        <v>6536573</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5831,13 +5825,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635118</t>
+          <t>https://artportalen.se/Sighting/120635096</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120635184</v>
+        <v>120635118</v>
       </c>
       <c r="B45" t="n">
         <v>5179</v>
@@ -5881,10 +5875,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>517640</v>
+        <v>517614</v>
       </c>
       <c r="R45" t="n">
-        <v>6536207</v>
+        <v>6536378</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5953,38 +5947,38 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635184</t>
+          <t>https://artportalen.se/Sighting/120635118</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120635188</v>
+        <v>120635184</v>
       </c>
       <c r="B46" t="n">
-        <v>5495</v>
+        <v>5179</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101410</v>
+        <v>100526</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5993,7 +5987,7 @@
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -6003,10 +5997,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>517619</v>
+        <v>517640</v>
       </c>
       <c r="R46" t="n">
-        <v>6536148</v>
+        <v>6536207</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6075,16 +6069,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635188</t>
+          <t>https://artportalen.se/Sighting/120635184</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120635114</v>
+        <v>120635188</v>
       </c>
       <c r="B47" t="n">
-        <v>5178</v>
+        <v>5495</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6092,21 +6086,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>102204</v>
+        <v>101410</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6121,14 +6115,14 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Molångskärret, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>517596</v>
+        <v>517619</v>
       </c>
       <c r="R47" t="n">
-        <v>6536395</v>
+        <v>6536148</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6197,38 +6191,38 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635114</t>
+          <t>https://artportalen.se/Sighting/120635188</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120635124</v>
+        <v>120635114</v>
       </c>
       <c r="B48" t="n">
-        <v>4781</v>
+        <v>5178</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>102306</v>
+        <v>102204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Grönhjon</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Callidium aeneum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(De Geer, 1775)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6237,20 +6231,20 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Molångskärret, Nrk</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>517623</v>
+        <v>517596</v>
       </c>
       <c r="R48" t="n">
-        <v>6536362</v>
+        <v>6536395</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6295,11 +6289,6 @@
           <t>16:00</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>kläckhål</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6324,16 +6313,16 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635124</t>
+          <t>https://artportalen.se/Sighting/120635114</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120635104</v>
+        <v>120635124</v>
       </c>
       <c r="B49" t="n">
-        <v>5199</v>
+        <v>4781</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6341,21 +6330,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105930</v>
+        <v>102306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Duftschmid, 1825)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6364,20 +6353,20 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>517609</v>
+        <v>517623</v>
       </c>
       <c r="R49" t="n">
-        <v>6536542</v>
+        <v>6536362</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6422,6 +6411,11 @@
           <t>16:00</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>kläckhål</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6446,13 +6440,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635104</t>
+          <t>https://artportalen.se/Sighting/120635124</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120635119</v>
+        <v>120635104</v>
       </c>
       <c r="B50" t="n">
         <v>5199</v>
@@ -6486,20 +6480,20 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>517619</v>
+        <v>517609</v>
       </c>
       <c r="R50" t="n">
-        <v>6536384</v>
+        <v>6536542</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6568,13 +6562,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635119</t>
+          <t>https://artportalen.se/Sighting/120635104</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120635176</v>
+        <v>120635119</v>
       </c>
       <c r="B51" t="n">
         <v>5199</v>
@@ -6608,7 +6602,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6618,10 +6612,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>517661</v>
+        <v>517619</v>
       </c>
       <c r="R51" t="n">
-        <v>6536283</v>
+        <v>6536384</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6690,13 +6684,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635176</t>
+          <t>https://artportalen.se/Sighting/120635119</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120635190</v>
+        <v>120635176</v>
       </c>
       <c r="B52" t="n">
         <v>5199</v>
@@ -6740,10 +6734,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>517634</v>
+        <v>517661</v>
       </c>
       <c r="R52" t="n">
-        <v>6536147</v>
+        <v>6536283</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6812,16 +6806,16 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635190</t>
+          <t>https://artportalen.se/Sighting/120635176</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120635112</v>
+        <v>120635190</v>
       </c>
       <c r="B53" t="n">
-        <v>97983</v>
+        <v>5199</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6829,42 +6823,43 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>105930</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Brattbrodalen, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>517607</v>
+        <v>517634</v>
       </c>
       <c r="R53" t="n">
-        <v>6536479</v>
+        <v>6536147</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6933,58 +6928,59 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635112</t>
+          <t>https://artportalen.se/Sighting/120635190</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120635183</v>
+        <v>120635112</v>
       </c>
       <c r="B54" t="n">
-        <v>79085</v>
+        <v>97983</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Uvstensberget, Nrk</t>
+          <t>Brattbrodalen, Nrk</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>517625</v>
+        <v>517607</v>
       </c>
       <c r="R54" t="n">
-        <v>6536200</v>
+        <v>6536479</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7053,63 +7049,61 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120635183</t>
+          <t>https://artportalen.se/Sighting/120635112</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>132585613</v>
+        <v>120635183</v>
       </c>
       <c r="B55" t="n">
-        <v>40305</v>
+        <v>79085</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>214803</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dolkstekelsglasvinge</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Synanthedon scoliaeformis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Borkhausen, 1789)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Kortorpa mosse, Nrk</t>
+          <t>Uvstensberget, Nrk</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>515594</v>
+        <v>517625</v>
       </c>
       <c r="R55" t="n">
-        <v>6537089</v>
+        <v>6536200</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7133,12 +7127,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7165,51 +7169,60 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132585613</t>
+          <t>https://artportalen.se/Sighting/120635183</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>85451244</v>
+        <v>132585613</v>
       </c>
       <c r="B56" t="n">
-        <v>97358</v>
+        <v>40305</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>53</v>
+        <v>214803</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dolkstekelsglasvinge</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Synanthedon scoliaeformis</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Borkhausen, 1789)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Kortorpa mosse, Nrk</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519672</v>
+        <v>515594</v>
       </c>
       <c r="R56" t="n">
-        <v>6532590</v>
+        <v>6537089</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7236,12 +7249,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7250,30 +7263,31 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451244</t>
+          <t>https://artportalen.se/Sighting/132585613</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>85451245</v>
+        <v>85451244</v>
       </c>
       <c r="B57" t="n">
         <v>97358</v>
@@ -7308,10 +7322,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519625</v>
+        <v>519672</v>
       </c>
       <c r="R57" t="n">
-        <v>6532581</v>
+        <v>6532590</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7369,16 +7383,16 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451245</t>
+          <t>https://artportalen.se/Sighting/85451244</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>55321736</v>
+        <v>85451245</v>
       </c>
       <c r="B58" t="n">
-        <v>78993</v>
+        <v>97358</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7386,41 +7400,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519636</v>
+        <v>519625</v>
       </c>
       <c r="R58" t="n">
-        <v>6532709</v>
+        <v>6532581</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7444,17 +7454,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7467,72 +7472,71 @@
         <v>0</v>
       </c>
       <c r="AT58" t="inlineStr"/>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55321736</t>
+          <t>https://artportalen.se/Sighting/85451245</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>85451302</v>
+        <v>55321736</v>
       </c>
       <c r="B59" t="n">
-        <v>96458</v>
+        <v>78993</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2818</v>
+        <v>353</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519731</v>
+        <v>519636</v>
       </c>
       <c r="R59" t="n">
-        <v>6532645</v>
+        <v>6532709</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7556,12 +7560,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7574,29 +7583,34 @@
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451302</t>
+          <t>https://artportalen.se/Sighting/55321736</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>85451356</v>
+        <v>85451302</v>
       </c>
       <c r="B60" t="n">
-        <v>92333</v>
+        <v>96458</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7604,21 +7618,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4217</v>
+        <v>2818</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7628,10 +7642,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519697</v>
+        <v>519731</v>
       </c>
       <c r="R60" t="n">
-        <v>6532776</v>
+        <v>6532645</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7689,54 +7703,54 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451356</t>
+          <t>https://artportalen.se/Sighting/85451302</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>54013950</v>
+        <v>85451356</v>
       </c>
       <c r="B61" t="n">
-        <v>93197</v>
+        <v>92333</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519596</v>
+        <v>519697</v>
       </c>
       <c r="R61" t="n">
-        <v>6532710</v>
+        <v>6532776</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7760,12 +7774,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7777,28 +7791,27 @@
       <c r="AG61" t="b">
         <v>0</v>
       </c>
-      <c r="AR61" t="inlineStr"/>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54013950</t>
+          <t>https://artportalen.se/Sighting/85451356</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>81095228</v>
+        <v>54013950</v>
       </c>
       <c r="B62" t="n">
         <v>93197</v>
@@ -7829,14 +7842,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hjärtasjön med omnejd, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519615</v>
+        <v>519596</v>
       </c>
       <c r="R62" t="n">
-        <v>6532734</v>
+        <v>6532710</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7863,12 +7876,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7880,65 +7893,66 @@
       <c r="AG62" t="b">
         <v>0</v>
       </c>
+      <c r="AR62" t="inlineStr"/>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/81095228</t>
+          <t>https://artportalen.se/Sighting/54013950</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>54013984</v>
+        <v>81095228</v>
       </c>
       <c r="B63" t="n">
-        <v>91282</v>
+        <v>93197</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5685</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>Hjärtasjön med omnejd, Nrk</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519636</v>
+        <v>519615</v>
       </c>
       <c r="R63" t="n">
-        <v>6532709</v>
+        <v>6532734</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7965,12 +7979,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7982,76 +7996,68 @@
       <c r="AG63" t="b">
         <v>0</v>
       </c>
-      <c r="AR63" t="inlineStr"/>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54013984</t>
+          <t>https://artportalen.se/Sighting/81095228</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>132028911</v>
+        <v>54013984</v>
       </c>
       <c r="B64" t="n">
-        <v>79373</v>
+        <v>91282</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bavlingeskogen, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519619</v>
+        <v>519636</v>
       </c>
       <c r="R64" t="n">
-        <v>6532722</v>
+        <v>6532709</v>
       </c>
       <c r="S64" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8075,12 +8081,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-02-22</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8089,76 +8095,79 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
+      <c r="AR64" t="inlineStr"/>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Per Karlsson Linderum</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132028911</t>
+          <t>https://artportalen.se/Sighting/54013984</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>55321959</v>
+        <v>132028911</v>
       </c>
       <c r="B65" t="n">
-        <v>79946</v>
+        <v>79373</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>Bavlingeskogen, Nrk</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519636</v>
+        <v>519619</v>
       </c>
       <c r="R65" t="n">
-        <v>6532709</v>
+        <v>6532722</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8182,17 +8191,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2026-02-22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8201,35 +8205,31 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Per Karlsson Linderum</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55321959</t>
+          <t>https://artportalen.se/Sighting/132028911</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>55321978</v>
+        <v>55321959</v>
       </c>
       <c r="B66" t="n">
         <v>79946</v>
@@ -8268,10 +8268,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519596</v>
+        <v>519636</v>
       </c>
       <c r="R66" t="n">
-        <v>6532710</v>
+        <v>6532709</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8339,13 +8339,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55321978</t>
+          <t>https://artportalen.se/Sighting/55321959</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>55322041</v>
+        <v>55321978</v>
       </c>
       <c r="B67" t="n">
         <v>79946</v>
@@ -8384,10 +8384,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519628</v>
+        <v>519596</v>
       </c>
       <c r="R67" t="n">
-        <v>6532734</v>
+        <v>6532710</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8424,7 +8424,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Observerad av Toni Berglund</t>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8455,13 +8455,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55322041</t>
+          <t>https://artportalen.se/Sighting/55321978</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>85451274</v>
+        <v>55322041</v>
       </c>
       <c r="B68" t="n">
         <v>79946</v>
@@ -8489,20 +8489,24 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519738</v>
+        <v>519628</v>
       </c>
       <c r="R68" t="n">
-        <v>6532781</v>
+        <v>6532734</v>
       </c>
       <c r="S68" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8526,12 +8530,17 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Observerad av Toni Berglund</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8544,29 +8553,34 @@
         <v>0</v>
       </c>
       <c r="AT68" t="inlineStr"/>
+      <c r="AU68" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451274</t>
+          <t>https://artportalen.se/Sighting/55322041</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>85451350</v>
+        <v>85451274</v>
       </c>
       <c r="B69" t="n">
-        <v>78993</v>
+        <v>79946</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8574,21 +8588,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8598,10 +8612,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520143</v>
+        <v>519738</v>
       </c>
       <c r="R69" t="n">
-        <v>6532731</v>
+        <v>6532781</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8659,16 +8673,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451350</t>
+          <t>https://artportalen.se/Sighting/85451274</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>85451285</v>
+        <v>85451350</v>
       </c>
       <c r="B70" t="n">
-        <v>79946</v>
+        <v>78993</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8676,21 +8690,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8700,10 +8714,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520192</v>
+        <v>520143</v>
       </c>
       <c r="R70" t="n">
-        <v>6532728</v>
+        <v>6532731</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8761,13 +8775,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451285</t>
+          <t>https://artportalen.se/Sighting/85451350</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>85451403</v>
+        <v>85451285</v>
       </c>
       <c r="B71" t="n">
         <v>79946</v>
@@ -8798,14 +8812,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>ost Bavlingssjön, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520311</v>
+        <v>520192</v>
       </c>
       <c r="R71" t="n">
-        <v>6532603</v>
+        <v>6532728</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8863,54 +8877,54 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451403</t>
+          <t>https://artportalen.se/Sighting/85451285</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>80563800</v>
+        <v>85451403</v>
       </c>
       <c r="B72" t="n">
-        <v>93193</v>
+        <v>79946</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>4363</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>ost Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519723</v>
+        <v>520311</v>
       </c>
       <c r="R72" t="n">
-        <v>6531341</v>
+        <v>6532603</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8934,12 +8948,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8954,49 +8968,49 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563800</t>
+          <t>https://artportalen.se/Sighting/85451403</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>80563801</v>
+        <v>80563800</v>
       </c>
       <c r="B73" t="n">
-        <v>93197</v>
+        <v>93193</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>4363</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9006,10 +9020,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519697</v>
+        <v>519723</v>
       </c>
       <c r="R73" t="n">
-        <v>6531333</v>
+        <v>6531341</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9067,13 +9081,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563801</t>
+          <t>https://artportalen.se/Sighting/80563800</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>80563803</v>
+        <v>80563801</v>
       </c>
       <c r="B74" t="n">
         <v>93197</v>
@@ -9108,10 +9122,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519682</v>
+        <v>519697</v>
       </c>
       <c r="R74" t="n">
-        <v>6531348</v>
+        <v>6531333</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9169,13 +9183,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563803</t>
+          <t>https://artportalen.se/Sighting/80563801</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>80563804</v>
+        <v>80563803</v>
       </c>
       <c r="B75" t="n">
         <v>93197</v>
@@ -9210,10 +9224,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519675</v>
+        <v>519682</v>
       </c>
       <c r="R75" t="n">
-        <v>6531363</v>
+        <v>6531348</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9271,13 +9285,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563804</t>
+          <t>https://artportalen.se/Sighting/80563803</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>80563805</v>
+        <v>80563804</v>
       </c>
       <c r="B76" t="n">
         <v>93197</v>
@@ -9312,10 +9326,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519682</v>
+        <v>519675</v>
       </c>
       <c r="R76" t="n">
-        <v>6531371</v>
+        <v>6531363</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9373,51 +9387,51 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563805</t>
+          <t>https://artportalen.se/Sighting/80563804</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>54014169</v>
+        <v>80563805</v>
       </c>
       <c r="B77" t="n">
-        <v>91872</v>
+        <v>93197</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519821</v>
+        <v>519682</v>
       </c>
       <c r="R77" t="n">
-        <v>6531449</v>
+        <v>6531371</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9444,12 +9458,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2011-08-25</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9461,28 +9475,27 @@
       <c r="AG77" t="b">
         <v>0</v>
       </c>
-      <c r="AR77" t="inlineStr"/>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/54014169</t>
+          <t>https://artportalen.se/Sighting/80563805</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>85451261</v>
+        <v>54014169</v>
       </c>
       <c r="B78" t="n">
         <v>91872</v>
@@ -9513,17 +9526,17 @@
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Lerbäck, , Nrk</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519855</v>
+        <v>519821</v>
       </c>
       <c r="R78" t="n">
-        <v>6531422</v>
+        <v>6531449</v>
       </c>
       <c r="S78" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9547,12 +9560,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2011-08-25</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9564,72 +9577,69 @@
       <c r="AG78" t="b">
         <v>0</v>
       </c>
+      <c r="AR78" t="inlineStr"/>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85451261</t>
+          <t>https://artportalen.se/Sighting/54014169</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>55322013</v>
+        <v>85451261</v>
       </c>
       <c r="B79" t="n">
-        <v>79946</v>
+        <v>91872</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
+          <t>väst Bavlingssjön, Nrk</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519789</v>
+        <v>519855</v>
       </c>
       <c r="R79" t="n">
-        <v>6531472</v>
+        <v>6531422</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9653,17 +9663,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2011-05-09</t>
+          <t>2020-05-03</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2011-08-29</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Observerad av Olli Manninen</t>
+          <t>2020-05-15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9676,31 +9681,26 @@
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Viktor Säfve</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/55322013</t>
+          <t>https://artportalen.se/Sighting/85451261</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>80563802</v>
+        <v>55322013</v>
       </c>
       <c r="B80" t="n">
         <v>79946</v>
@@ -9728,17 +9728,21 @@
           <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
+          <t>Naturskogar Hjärta-, Bavlings- och Östersjön - Haddebo kronopark, Nrk</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519687</v>
+        <v>519789</v>
       </c>
       <c r="R80" t="n">
-        <v>6531345</v>
+        <v>6531472</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9765,12 +9769,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2019-09-26</t>
+          <t>2011-05-09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2019-09-29</t>
+          <t>2011-08-29</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Observerad av Olli Manninen</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9782,32 +9791,32 @@
       <c r="AG80" t="b">
         <v>0</v>
       </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>silverstubbe</t>
-        </is>
-      </c>
       <c r="AT80" t="inlineStr"/>
+      <c r="AU80" t="inlineStr">
+        <is>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Viktor Säfve</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80563802</t>
+          <t>https://artportalen.se/Sighting/55322013</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>85451281</v>
+        <v>80563802</v>
       </c>
       <c r="B81" t="n">
         <v>79946</v>
@@ -9838,17 +9847,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>väst Bavlingssjön, Nrk</t>
+          <t>kring Hjärtasjön-Bavlingsjön, Nrk</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>519882</v>
+        <v>519687</v>
       </c>
       <c r="R81" t="n">
-        <v>6531425</v>
+        <v>6531345</v>
       </c>
       <c r="S81" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9872,12 +9881,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2020-05-03</t>
+          <t>2019-09-26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2020-05-15</t>
+          <t>2019-09-29</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9888,20 +9897,127 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>silverstubbe</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Mikael Hagström</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80563802</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>85451281</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>väst Bavlingssjön, Nrk</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>519882</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6531425</v>
+      </c>
+      <c r="S82" t="n">
+        <v>25</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Hallsberg</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Svennevad</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2020-05-03</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2020-05-15</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/85451281</t>
         </is>
@@ -9989,6 +10105,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -2222,7 +2222,7 @@
         <v>134855725</v>
       </c>
       <c r="B15" t="n">
-        <v>99191</v>
+        <v>99193</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 1157-2022 artfynd.xlsx
+++ b/artfynd/S 1157-2022 artfynd.xlsx
@@ -2222,7 +2222,7 @@
         <v>134855725</v>
       </c>
       <c r="B15" t="n">
-        <v>99193</v>
+        <v>99210</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
